--- a/ig/TEST-SUPPLEMENT/ValueSet-JDV-J209-TypeSavoirFaire-ROR.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-JDV-J209-TypeSavoirFaire-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250625120000</t>
+    <t>20251016120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T12:00:00+01:00</t>
+    <t>2025-10-16T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,7 +102,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>Compétence</t>
+    <t>Compétence de médecine</t>
   </si>
   <si>
     <t>CAPA</t>
